--- a/donnees.xlsx
+++ b/donnees.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C183051-8FAE-4B99-B136-C244238CCEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D5FF20-792D-463A-BCAB-E33AC54DDF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{087A1B5B-7B97-4327-AC94-7D0ECF997B43}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{087A1B5B-7B97-4327-AC94-7D0ECF997B43}"/>
   </bookViews>
   <sheets>
     <sheet name="Approche déterministe" sheetId="1" r:id="rId1"/>
@@ -515,6 +515,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -524,10 +528,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -852,12 +852,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="28"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="32"/>
       <c r="F2" s="25"/>
       <c r="G2" s="25"/>
     </row>
@@ -1002,10 +1002,10 @@
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="28"/>
+      <c r="C16" s="32"/>
       <c r="D16" s="25"/>
       <c r="E16" s="25"/>
     </row>
@@ -1042,22 +1042,22 @@
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="27"/>
+      <c r="C23" s="31"/>
       <c r="D23" s="12">
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="28"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="32"/>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
     </row>
@@ -1203,162 +1203,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="C1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="32"/>
+      <c r="D1" s="29"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="30">
+      <c r="C2" s="27">
         <f>'Approche déterministe'!C4</f>
         <v>10</v>
       </c>
-      <c r="D2" s="32"/>
+      <c r="D2" s="29"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="30">
+      <c r="C3" s="27">
         <f>'Approche déterministe'!D4</f>
         <v>5</v>
       </c>
-      <c r="D3" s="32"/>
+      <c r="D3" s="29"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="27">
         <f>'Approche déterministe'!E4</f>
         <v>3</v>
       </c>
-      <c r="D4" s="32"/>
+      <c r="D4" s="29"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="27">
         <f>'Approche déterministe'!C5</f>
         <v>8</v>
       </c>
-      <c r="D5" s="32"/>
+      <c r="D5" s="29"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="27">
         <f>'Approche déterministe'!D5</f>
         <v>6</v>
       </c>
-      <c r="D6" s="32"/>
+      <c r="D6" s="29"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="27">
         <f>'Approche déterministe'!E5</f>
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="27">
         <f>'Approche déterministe'!C6</f>
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="31" t="s">
+      <c r="A9" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="27">
         <f>'Approche déterministe'!D6</f>
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="27">
         <f>'Approche déterministe'!E6</f>
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="s">
+      <c r="A11" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="30" t="s">
+      <c r="B11" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="27">
         <f>'Approche déterministe'!C7</f>
         <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="31" t="s">
+      <c r="A12" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="30" t="s">
+      <c r="B12" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="27">
         <f>'Approche déterministe'!D7</f>
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="31" t="s">
+      <c r="A13" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="27">
         <f>'Approche déterministe'!E7</f>
         <v>2</v>
       </c>
@@ -1622,15 +1622,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A2A049104A612744BD1BD51322DDA00D" ma:contentTypeVersion="3" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="4edfbcde0d7735c9757274b6cde66ba3">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f4900802-4956-4843-8cbf-7f37431657c7" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c5fdc8ffbc604ecca05edfe330a2a2f8" ns2:_="">
     <xsd:import namespace="f4900802-4956-4843-8cbf-7f37431657c7"/>
@@ -1768,6 +1759,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7E1FD38-078D-4B89-8FA9-50A9148E2781}">
   <ds:schemaRefs>
@@ -1785,14 +1785,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92DDC23A-F33A-49C8-BA39-976AEA609D41}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1EAFDFB-EB5C-4754-816F-0F42621CC020}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1808,4 +1800,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92DDC23A-F33A-49C8-BA39-976AEA609D41}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/donnees.xlsx
+++ b/donnees.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="121" documentId="13_ncr:1_{65D5FF20-792D-463A-BCAB-E33AC54DDF81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C847F1E-AA76-4BC9-AC8E-9F31FF1A9DA6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0D727E-A0CF-45D3-AC3C-DDD1B397F7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10200" yWindow="96" windowWidth="12936" windowHeight="12240" tabRatio="794" firstSheet="5" activeTab="6" xr2:uid="{087A1B5B-7B97-4327-AC94-7D0ECF997B43}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="794" activeTab="1" xr2:uid="{087A1B5B-7B97-4327-AC94-7D0ECF997B43}"/>
   </bookViews>
   <sheets>
     <sheet name="Approche déterministe" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="42">
   <si>
     <t>Demande</t>
   </si>
@@ -133,6 +133,36 @@
   </si>
   <si>
     <t>Probabilite</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -170,7 +200,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -550,11 +580,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -582,6 +632,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -591,12 +647,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -921,12 +973,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="29"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="7" t="s">
@@ -1069,10 +1121,10 @@
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="29"/>
+      <c r="C16" s="35"/>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="7" t="s">
@@ -1107,22 +1159,22 @@
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="28"/>
+      <c r="C23" s="34"/>
       <c r="D23" s="12">
         <v>0.55000000000000004</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="29"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="35"/>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="7" t="s">
@@ -1259,7 +1311,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E7AEEC9-353D-473A-9ADB-652C7A77150E}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.44140625" customWidth="1"/>
@@ -1419,6 +1471,372 @@
         <f>'Approche déterministe'!E7</f>
         <v>2</v>
       </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C26">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C38">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C39">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" s="36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A44" s="36"/>
+      <c r="B44" s="26"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A45" s="36"/>
+      <c r="B45" s="26"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A46" s="36"/>
+      <c r="B46" s="26"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A47" s="36"/>
+      <c r="B47" s="26"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A48" s="36"/>
+      <c r="B48" s="26"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" s="36"/>
+      <c r="B49" s="26"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B50" s="26"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B51" s="26"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B52" s="26"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B53" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1493,7 +1911,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="3">
-        <v>30</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -1501,7 +1919,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1509,7 +1927,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="6">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1519,7 +1937,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49F16090-0968-47E1-8D71-17427DA9CED4}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1590,6 +2008,146 @@
       </c>
       <c r="D5" s="6">
         <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6">
+        <v>20</v>
+      </c>
+      <c r="D6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7">
+        <v>50</v>
+      </c>
+      <c r="D7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8">
+        <v>70</v>
+      </c>
+      <c r="D8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10">
+        <v>60</v>
+      </c>
+      <c r="D10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11">
+        <v>90</v>
+      </c>
+      <c r="D11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12">
+        <v>25</v>
+      </c>
+      <c r="D12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13">
+        <v>85</v>
+      </c>
+      <c r="D13">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14">
+        <v>55</v>
+      </c>
+      <c r="D14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15">
+        <v>75</v>
+      </c>
+      <c r="D15">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1599,10 +2157,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67873F19-09DB-4B30-B661-24661F264597}">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>17</v>
       </c>
@@ -1618,8 +2176,38 @@
       <c r="E1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1633,7 +2221,7 @@
         <v>40.040604391042855</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1647,7 +2235,7 @@
         <v>33.455193916640212</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1661,18 +2249,68 @@
         <v>29.618406439239774</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5">
-        <v>40.040604391042855</v>
+        <v>40.040604391042898</v>
       </c>
       <c r="C5">
         <v>33.455193916640212</v>
       </c>
       <c r="D5">
         <v>29.618406439239774</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1702,18 +2340,18 @@
       <c r="C1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="E1" s="34" t="s">
+      <c r="E1" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="26" t="s">
@@ -2005,18 +2643,18 @@
     </row>
     <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="17" spans="4:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="29" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="28">
         <v>0.25</v>
       </c>
     </row>
@@ -2042,12 +2680,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2189,15 +2824,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92DDC23A-F33A-49C8-BA39-976AEA609D41}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7E1FD38-078D-4B89-8FA9-50A9148E2781}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f4900802-4956-4843-8cbf-7f37431657c7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2221,17 +2867,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7E1FD38-078D-4B89-8FA9-50A9148E2781}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92DDC23A-F33A-49C8-BA39-976AEA609D41}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f4900802-4956-4843-8cbf-7f37431657c7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>